--- a/data/trans_orig/IP04D$individual-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$individual-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31575</t>
+          <t>32489</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49139</t>
+          <t>49222</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47399</t>
+          <t>46913</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66375</t>
+          <t>66632</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84144</t>
+          <t>84121</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110663</t>
+          <t>109871</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,91%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95314</t>
+          <t>95231</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112878</t>
+          <t>111964</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78987</t>
+          <t>78730</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97963</t>
+          <t>98449</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179151</t>
+          <t>179943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>205670</t>
+          <t>205693</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53487</t>
+          <t>54071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76053</t>
+          <t>76673</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60881</t>
+          <t>60393</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85349</t>
+          <t>85823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>121130</t>
+          <t>120892</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155162</t>
+          <t>155428</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160197</t>
+          <t>159577</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>182763</t>
+          <t>182179</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>182988</t>
+          <t>182514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>207456</t>
+          <t>207944</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349425</t>
+          <t>349159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>383457</t>
+          <t>383695</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,04%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39272</t>
+          <t>39169</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57554</t>
+          <t>58033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43854</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64118</t>
+          <t>63305</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88355</t>
+          <t>88569</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115490</t>
+          <t>116657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98699</t>
+          <t>98220</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116981</t>
+          <t>117084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94453</t>
+          <t>95266</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114717</t>
+          <t>115132</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>199334</t>
+          <t>198167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>226469</t>
+          <t>226255</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36843</t>
+          <t>36606</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57888</t>
+          <t>55834</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45010</t>
+          <t>45568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65234</t>
+          <t>65609</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87714</t>
+          <t>87543</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115718</t>
+          <t>116089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113449</t>
+          <t>115503</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134494</t>
+          <t>134731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114721</t>
+          <t>114346</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134945</t>
+          <t>134387</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235574</t>
+          <t>235203</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>263578</t>
+          <t>263749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181701</t>
+          <t>179896</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>221031</t>
+          <t>219776</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>217052</t>
+          <t>217360</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>258778</t>
+          <t>259166</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>407801</t>
+          <t>409122</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>466932</t>
+          <t>467887</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>487261</t>
+          <t>488516</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>526591</t>
+          <t>528396</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>493447</t>
+          <t>493059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>535173</t>
+          <t>534865</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>993585</t>
+          <t>992630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1052716</t>
+          <t>1051395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,99%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25909</t>
+          <t>26231</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41207</t>
+          <t>41457</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28448</t>
+          <t>28636</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57811</t>
+          <t>58089</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81635</t>
+          <t>80019</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90447</t>
+          <t>90197</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105745</t>
+          <t>105423</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80397</t>
+          <t>79220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95716</t>
+          <t>95528</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174183</t>
+          <t>175799</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>198007</t>
+          <t>197729</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,29%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67492</t>
+          <t>66050</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89569</t>
+          <t>89124</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62142</t>
+          <t>61472</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85744</t>
+          <t>84866</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135441</t>
+          <t>136971</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>167894</t>
+          <t>169372</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118879</t>
+          <t>119324</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>140956</t>
+          <t>142398</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>170340</t>
+          <t>171218</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>193942</t>
+          <t>194612</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296638</t>
+          <t>295160</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>329091</t>
+          <t>327561</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,51%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>46370</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66869</t>
+          <t>66943</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45552</t>
+          <t>46390</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65623</t>
+          <t>66466</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98291</t>
+          <t>95606</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129193</t>
+          <t>125593</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120571</t>
+          <t>120497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141068</t>
+          <t>141070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120764</t>
+          <t>119921</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140835</t>
+          <t>139997</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244634</t>
+          <t>248234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>275536</t>
+          <t>278221</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44652</t>
+          <t>46041</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66453</t>
+          <t>65577</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38332</t>
+          <t>38172</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58992</t>
+          <t>57668</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89732</t>
+          <t>89619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118866</t>
+          <t>118438</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106185</t>
+          <t>107061</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127986</t>
+          <t>126597</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114385</t>
+          <t>115709</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>135045</t>
+          <t>135205</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>227149</t>
+          <t>227577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>256283</t>
+          <t>256396</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>202173</t>
+          <t>203027</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>242461</t>
+          <t>242223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>190319</t>
+          <t>193406</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>232392</t>
+          <t>234009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409889</t>
+          <t>405192</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>465742</t>
+          <t>463161</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>457720</t>
+          <t>457958</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498008</t>
+          <t>497154</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>507619</t>
+          <t>506002</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>549692</t>
+          <t>546605</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>974450</t>
+          <t>977031</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1030303</t>
+          <t>1035000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20751</t>
+          <t>21205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18855</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32501</t>
+          <t>33176</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42743</t>
+          <t>43100</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51146</t>
+          <t>51409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40693</t>
+          <t>40239</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51149</t>
+          <t>51271</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86454</t>
+          <t>85779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100100</t>
+          <t>100358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19815</t>
+          <t>19711</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35310</t>
+          <t>35845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22285</t>
+          <t>22207</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40578</t>
+          <t>41048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46987</t>
+          <t>46388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70233</t>
+          <t>71399</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>123989</t>
+          <t>123454</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139484</t>
+          <t>139588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>141269</t>
+          <t>140799</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159562</t>
+          <t>159640</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>270914</t>
+          <t>269748</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>294160</t>
+          <t>294759</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>18020</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35236</t>
+          <t>34453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>32973</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56829</t>
+          <t>55031</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55622</t>
+          <t>57158</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83688</t>
+          <t>85314</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>138652</t>
+          <t>139435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>155725</t>
+          <t>155868</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154718</t>
+          <t>156516</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>178051</t>
+          <t>178574</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301746</t>
+          <t>300120</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329812</t>
+          <t>328276</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30778</t>
+          <t>30983</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57976</t>
+          <t>59158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51493</t>
+          <t>48532</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99690</t>
+          <t>98148</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90666</t>
+          <t>89050</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146941</t>
+          <t>141768</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>216482</t>
+          <t>215300</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>243680</t>
+          <t>243475</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>205793</t>
+          <t>207335</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>253990</t>
+          <t>256951</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>433000</t>
+          <t>438173</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>489275</t>
+          <t>490891</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87393</t>
+          <t>89346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123999</t>
+          <t>126675</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>134069</t>
+          <t>134546</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>191362</t>
+          <t>189991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>234280</t>
+          <t>232576</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>303437</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>541157</t>
+          <t>538481</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>577763</t>
+          <t>575810</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>568960</t>
+          <t>570331</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>626253</t>
+          <t>625776</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1122040</t>
+          <t>1124560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1191197</t>
+          <t>1192901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$individual-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$individual-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56441</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>46912</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>66154</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>32,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45,51%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32489</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>49222</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>32343</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>50005</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>28,09%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,49%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>34,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>56441</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>46913</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>66632</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>38,83%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84121</t>
+          <t>83252</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109871</t>
+          <t>110779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>88921</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>79208</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>98450</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>61,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>54,49%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>67,73%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>103878</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>95231</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>111964</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>94448</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>112110</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>71,91%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>65,93%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>77,51%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>88921</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>78730</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>98449</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>61,17%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179943</t>
+          <t>179035</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>205693</t>
+          <t>206562</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,27%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145362</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145362</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145362</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>144453</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>144453</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>144453</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145362</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145362</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145362</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>73252</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>60444</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86060</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>27,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22,53%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>32,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>64646</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54071</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>76673</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>54435</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>77082</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>27,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,89%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>73252</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>60393</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>85823</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>27,3%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120892</t>
+          <t>122508</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155428</t>
+          <t>154554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>195085</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>182277</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>207893</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>72,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>67,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>77,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>171604</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>159577</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>182179</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>159168</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>181815</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>72,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>195085</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>182514</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>207944</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>72,7%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349159</t>
+          <t>350033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>383695</t>
+          <t>382079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,72%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268337</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268337</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268337</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268337</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268337</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53346</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>43654</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>64534</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>33,64%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,53%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>40,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>48225</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>39169</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>58033</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>39349</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>57623</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>30,86%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>53346</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>43439</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>63305</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>33,64%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88569</t>
+          <t>88638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116657</t>
+          <t>115991</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>105225</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>94037</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>114917</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>66,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>59,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>72,47%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>108028</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>98220</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>117084</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>98630</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>116904</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>69,14%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>74,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>105225</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>95266</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>115132</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>66,36%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>198167</t>
+          <t>198833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>226255</t>
+          <t>226186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,85%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156253</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156253</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156253</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54982</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>45581</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65024</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>30,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36,13%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>46463</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>36606</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>55834</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>36367</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>56696</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>27,12%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>32,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>54982</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>45568</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>65609</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>30,55%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87543</t>
+          <t>87227</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116089</t>
+          <t>113686</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>124973</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>114931</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>134374</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>69,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63,87%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>74,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>124874</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>115503</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>134731</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>114641</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>134970</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>72,88%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>78,63%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>124973</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>114346</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>134387</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>69,45%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235203</t>
+          <t>237606</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>263749</t>
+          <t>264065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,17%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>238021</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>219149</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>259581</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31,64%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>34,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>287</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>199908</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>179896</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>219776</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>180444</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>219171</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>28,22%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,4%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,03%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>238021</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>217360</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>259166</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>31,64%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409122</t>
+          <t>409018</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>467887</t>
+          <t>467293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>514204</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>492644</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>533076</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>68,36%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>65,49%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>70,87%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>734</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>508384</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>488516</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>528396</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>489121</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>527848</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>71,78%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>68,97%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>74,6%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>730</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>514204</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>493059</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>534865</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>68,36%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>992630</t>
+          <t>993224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1051395</t>
+          <t>1051499</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,0%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1021</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35698</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28229</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>45295</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>28,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,74%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>36,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>33308</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26231</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>41457</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>26063</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>41026</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>25,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>35698</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>28636</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>44944</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>28,75%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58089</t>
+          <t>58199</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80019</t>
+          <t>80228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>88466</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>78869</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>95935</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>71,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>63,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77,26%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>98346</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>90197</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>105423</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>90628</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>105591</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>74,7%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>68,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>80,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>88466</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>79220</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>95528</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>71,25%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>175799</t>
+          <t>175590</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>197729</t>
+          <t>197619</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>73713</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>61182</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>85362</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>28,78%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23,89%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>33,33%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>77708</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>66050</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>89124</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>66701</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>88204</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>37,28%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>42,76%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>73713</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>61472</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>84866</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>28,78%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>136971</t>
+          <t>137250</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>169372</t>
+          <t>168892</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>182371</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>170722</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>194902</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>71,22%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>66,67%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>76,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>130740</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>119324</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>142398</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>120244</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>141747</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>62,72%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>57,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>68,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>182371</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>171218</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>194612</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>71,22%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295160</t>
+          <t>295640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>327561</t>
+          <t>327282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,45%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>256084</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>256084</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>256084</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>208448</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>208448</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>208448</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>256084</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>256084</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>256084</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>55402</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45119</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>66035</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>29,72%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>56011</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46370</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>66943</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>47350</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>67670</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>29,88%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>55402</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>46390</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>66466</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>29,72%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95606</t>
+          <t>97824</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125593</t>
+          <t>126641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>130985</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>120352</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>141268</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>70,28%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,79%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>131429</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>120497</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>141070</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>119770</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>140090</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>70,12%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>64,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>75,26%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>130985</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>119921</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>139997</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>70,28%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248234</t>
+          <t>247186</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>278221</t>
+          <t>276003</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>73,83%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186387</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186387</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186387</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>187440</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>187440</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>187440</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186387</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186387</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>47226</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37587</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>56892</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27,24%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21,68%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>32,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>55718</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>46041</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>65577</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>46402</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>66818</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>32,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>26,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>37,99%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>47226</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>38172</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>57668</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>27,24%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89619</t>
+          <t>89823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118438</t>
+          <t>117747</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>126151</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>116485</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>135790</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>72,76%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>67,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>78,32%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>116920</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>107061</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>126597</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>105820</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>126236</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>67,73%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>73,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>126151</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>115709</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>135205</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>72,76%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>227577</t>
+          <t>228268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>256396</t>
+          <t>256192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173377</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173377</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173377</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172638</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172638</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172638</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173377</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173377</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173377</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>212039</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>193026</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>230708</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>28,65%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,18%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>342</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>222745</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>203027</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>242223</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>202777</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>242038</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>31,81%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,59%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>212039</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>193406</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>234009</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>28,65%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>405192</t>
+          <t>406858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>463161</t>
+          <t>464447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>527972</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>509303</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>546985</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>71,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,82%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>73,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>713</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>477436</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>457958</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>497154</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>458143</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>497404</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>68,19%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>65,41%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>71,0%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>752</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>527972</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>506002</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>546605</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>71,35%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>977031</t>
+          <t>975745</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1035000</t>
+          <t>1033334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,75%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1055</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11628</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7636</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15755</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,01%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9739</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6102</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14411</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>25,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15221</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10173</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>24960</t>
+          <t>20491</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>15030</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33176</t>
+          <t>26459</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38909</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>34782</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>42901</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,99%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>47772</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>43100</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>51409</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>83,07%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>74,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46223</t>
+          <t>43227</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40239</t>
+          <t>39193</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51271</t>
+          <t>46783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>93995</t>
+          <t>82136</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85779</t>
+          <t>76168</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100358</t>
+          <t>87597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27706</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20334</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37578</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,95%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>27000</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>19711</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>35845</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,37%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30864</t>
+          <t>24915</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22207</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41048</t>
+          <t>33546</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>57864</t>
+          <t>52621</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46388</t>
+          <t>43214</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71399</t>
+          <t>64053</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>129199</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>119327</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>136571</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>82,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,05%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>132299</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>123454</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>139588</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>83,05%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,63%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>150983</t>
+          <t>120603</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140799</t>
+          <t>111972</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159640</t>
+          <t>126779</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>283283</t>
+          <t>249802</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>269748</t>
+          <t>238370</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>294759</t>
+          <t>259209</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156905</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156905</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156905</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341147</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341147</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341147</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40684</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30508</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>52208</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>25608</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18020</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34453</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,73%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>43611</t>
+          <t>26225</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32973</t>
+          <t>19009</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55031</t>
+          <t>36420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>69219</t>
+          <t>66909</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57158</t>
+          <t>53538</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85314</t>
+          <t>80797</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158485</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>146961</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>168661</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>148280</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>139435</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>155868</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>85,27%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>80,19%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,64%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>167936</t>
+          <t>149293</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156516</t>
+          <t>139098</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>178574</t>
+          <t>156509</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>316215</t>
+          <t>307777</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>300120</t>
+          <t>293889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328276</t>
+          <t>321148</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>63902</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>49789</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>91226</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21,84%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,17%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>45085</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30983</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>59158</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>16,43%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66619</t>
+          <t>46855</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48532</t>
+          <t>36573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98148</t>
+          <t>58789</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>111704</t>
+          <t>110757</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89050</t>
+          <t>92174</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141768</t>
+          <t>138209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>228743</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>201419</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>242856</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>78,16%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>82,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>229373</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>215300</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>243475</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>83,57%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>238864</t>
+          <t>208623</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207335</t>
+          <t>196689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>256951</t>
+          <t>218905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>468237</t>
+          <t>437365</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>438173</t>
+          <t>409913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>490891</t>
+          <t>455948</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>143920</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>123615</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>172157</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>20,58%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17,68%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24,62%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>107431</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>89346</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>126675</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>16,15%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,43%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,04%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>156315</t>
+          <t>106858</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>134546</t>
+          <t>92798</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189991</t>
+          <t>123777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>263747</t>
+          <t>250778</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>232576</t>
+          <t>224131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>300917</t>
+          <t>282524</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>555336</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>527099</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>575641</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>79,42%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>75,38%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>82,32%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>788</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>557725</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>538481</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>575810</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>83,85%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>80,96%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>86,57%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>604007</t>
+          <t>521745</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>570331</t>
+          <t>504826</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>625776</t>
+          <t>535805</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1161730</t>
+          <t>1077081</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1124560</t>
+          <t>1045335</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1192901</t>
+          <t>1103728</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
